--- a/output/pdf_financials_xlsx/DOL.xlsx
+++ b/output/pdf_financials_xlsx/DOL.xlsx
@@ -2383,10 +2383,10 @@
         <v>62.015</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>54.844</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>50.371</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>439.144</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>71.05800000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>101.261</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>122.685</v>
@@ -2473,10 +2473,10 @@
         <v>62.015</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>54.844</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>50.371</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2484,13 +2484,13 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>439.144</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>71.05800000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>101.261</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>122.685</v>
@@ -3013,10 +3013,10 @@
         <v>481.664</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>63.779</v>
+        <v>8.935</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>86.19199999999999</v>
+        <v>35.821</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -3024,13 +3024,13 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>449.161</v>
+        <v>10.017</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>100.18</v>
+        <v>29.122</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>143.485</v>
+        <v>42.224</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>110.862</v>
@@ -3999,19 +3999,19 @@
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>832.821</v>
+        <v>1876.9</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>257.674</v>
+        <v>1796.914</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>510.315</v>
+        <v>2251.903</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>273.771</v>
+        <v>2282.679</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>398.275</v>
+        <v>2625.121</v>
       </c>
     </row>
     <row r="70">
@@ -4089,19 +4089,19 @@
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>1014.714</v>
+        <v>2058.793</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>458.538</v>
+        <v>1997.778</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>729.122</v>
+        <v>2470.71</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>552.476</v>
+        <v>2561.384</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>776.018</v>
+        <v>3002.864</v>
       </c>
     </row>
     <row r="72">
@@ -4269,19 +4269,19 @@
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>53.379</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>170.228</v>
+        <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>96.89</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>106.93</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>110.395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4359,19 +4359,19 @@
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>1044.079</v>
+        <v>0</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>1539.24</v>
+        <v>0</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>1741.588</v>
+        <v>0</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>2008.908</v>
+        <v>0</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>2226.846</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4449,19 +4449,19 @@
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>1044.079</v>
+        <v>0</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>1539.24</v>
+        <v>0</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>1741.588</v>
+        <v>0</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>2008.908</v>
+        <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>2226.846</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4723,19 +4723,19 @@
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>1523.648</v>
+        <v>2567.727</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>1678.465</v>
+        <v>3217.705</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>1886.784</v>
+        <v>3628.372</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>2271.12</v>
+        <v>4280.028</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>2527.439</v>
+        <v>4754.285</v>
       </c>
     </row>
     <row r="86">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">

--- a/output/pdf_financials_xlsx/DOL.xlsx
+++ b/output/pdf_financials_xlsx/DOL.xlsx
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>2.267</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.737</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -5372,31 +5372,31 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>57.748</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>70.55</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>79.374</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>242.785</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>269.633</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>297.96</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>331.792</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>411.151</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>460.019</v>
       </c>
     </row>
     <row r="101">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -5912,31 +5912,31 @@
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.696</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.295</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.593</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.839</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.736</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="113">
@@ -30502,7 +30502,11 @@
           <t>Depreciation of property, plant and equipment, right-of-use assets and amortization of intangible assets 20</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -31608,7 +31612,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -31758,7 +31766,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -33010,7 +33022,11 @@
           <t>Depreciation of property, plant and equipment, right-of-use assets and amortization of intangible assets 17</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -33516,7 +33532,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -36684,7 +36704,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets 17</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -38110,7 +38134,11 @@
           <t>Additions to intangible assets 7</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -38786,7 +38814,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets 17</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -40588,7 +40620,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E451" s="5" t="n">
@@ -42004,7 +42036,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E470" s="5" t="n">
         <v>0.189</v>
       </c>
